--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_23.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_23.xlsx
@@ -471,74 +471,74 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>24756</v>
+        <v>84925</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alexandre da Paz</t>
+          <t>Renan Ramos</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45088</v>
+        <v>45100</v>
       </c>
       <c r="G2" t="n">
-        <v>3344.55</v>
+        <v>6629.96</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>59321</v>
+        <v>86945</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ana Beatriz da Cunha</t>
+          <t>Nicole Aragão</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45089</v>
+        <v>45101</v>
       </c>
       <c r="G3" t="n">
-        <v>5492.92</v>
+        <v>8634.77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>11730</v>
+        <v>49108</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Maria Sophia Costa</t>
+          <t>Antônio Santos</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vendas</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -547,51 +547,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45080</v>
+        <v>45086</v>
       </c>
       <c r="G4" t="n">
-        <v>9079.52</v>
+        <v>6608.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80512</v>
+        <v>9695</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maria Sophia Martins</t>
+          <t>Ana Júlia da Mata</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45084</v>
+        <v>45099</v>
       </c>
       <c r="G5" t="n">
-        <v>7057.88</v>
+        <v>5951.33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>60041</v>
+        <v>44451</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dr. Raul Ribeiro</t>
+          <t>Maria Alice Fernandes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -605,27 +605,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45085</v>
+        <v>45083</v>
       </c>
       <c r="G6" t="n">
-        <v>3331.19</v>
+        <v>7416.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>92089</v>
+        <v>21764</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Catarina Moraes</t>
+          <t>João Gabriel Costa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -637,53 +637,53 @@
         <v>3</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45103</v>
+        <v>45078</v>
       </c>
       <c r="G7" t="n">
-        <v>4858.56</v>
+        <v>6704.47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66154</v>
+        <v>96503</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Srta. Bruna Azevedo</t>
+          <t>Larissa Rocha</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Operações</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45085</v>
+        <v>45079</v>
       </c>
       <c r="G8" t="n">
-        <v>8883.049999999999</v>
+        <v>9464.360000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>52491</v>
+        <v>84669</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Felipe Pinto</t>
+          <t>João Guilherme da Cruz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -692,71 +692,71 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45100</v>
+        <v>45094</v>
       </c>
       <c r="G9" t="n">
-        <v>5469.08</v>
+        <v>2623.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>22720</v>
+        <v>32715</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Renan Fogaça</t>
+          <t>Luiz Miguel Fogaça</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45090</v>
+        <v>45103</v>
       </c>
       <c r="G10" t="n">
-        <v>12347.92</v>
+        <v>9157.639999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>64166</v>
+        <v>5370</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Augusto da Paz</t>
+          <t>Sarah Farias</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Operações</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45098</v>
+        <v>45106</v>
       </c>
       <c r="G11" t="n">
-        <v>7197.52</v>
+        <v>5447.94</v>
       </c>
     </row>
   </sheetData>
